--- a/data/Base colaboradores ativos.xlsx
+++ b/data/Base colaboradores ativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Log20\OneDrive\Área de Trabalho\GENTE\0. GESTÃO DE GENTE\Acomp. Área de Gente\Dashboard Python\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6859554D-5BE5-4E50-BC3E-18C4F55EF4CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F17A42A-4E65-430F-994E-A10CDD4C9F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$AF$1431</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$1:$AF$602</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69237,7 +69237,7 @@
       <c r="AF602" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF1431" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AF602" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>